--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486968_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486968_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8835</v>
+        <v>5.5236</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8162</v>
+        <v>2.6342</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0673</v>
+        <v>2.8895</v>
       </c>
       <c r="G2" t="n">
         <v>4.3482</v>
@@ -610,13 +610,13 @@
         <v>3.0801</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1258</v>
+        <v>-1.4857</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.868</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4398</v>
+        <v>-0.6177</v>
       </c>
       <c r="V2" t="n">
         <v>4.7145</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.09</v>
+        <v>3.352</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9258999999999999</v>
+        <v>1.7511</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1641</v>
+        <v>1.6009</v>
       </c>
       <c r="G3" t="n">
         <v>2.3254</v>
@@ -688,13 +688,13 @@
         <v>3.0801</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9952</v>
+        <v>-0.7331</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3097</v>
+        <v>-0.4845</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3145</v>
+        <v>-0.2487</v>
       </c>
       <c r="V3" t="n">
         <v>0.9384</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4025</v>
+        <v>2.8934</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5749</v>
+        <v>1.1251</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8276</v>
+        <v>1.7683</v>
       </c>
       <c r="G4" t="n">
         <v>1.2718</v>
@@ -766,13 +766,13 @@
         <v>2.6694</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.779</v>
+        <v>-1.2882</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2516</v>
+        <v>-0.7014</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5275</v>
+        <v>-0.5868</v>
       </c>
       <c r="V4" t="n">
         <v>0.2402</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6128</v>
+        <v>0.6357</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3179</v>
+        <v>-1.4728</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9307</v>
+        <v>2.1085</v>
       </c>
       <c r="G5" t="n">
         <v>-2.6797</v>
@@ -844,13 +844,13 @@
         <v>3.4908</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1716</v>
+        <v>-1.1487</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3102</v>
+        <v>-0.4652</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.6835</v>
       </c>
       <c r="V5" t="n">
         <v>1.1786</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>U. DÁMASO GONZÁLEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1849</v>
+        <v>0.1395</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3865</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5714</v>
+        <v>0.1395</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.8078</v>
+        <v>0.1395</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6422</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1656</v>
+        <v>0.1395</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.7064</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2589</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4476</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1014</v>
+        <v>0.1395</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3833</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7181</v>
+        <v>0.1395</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2588</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0461</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5465</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5926</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>2.9466</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>4.1252</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. DÁMASO GONZÁLEZ</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1395</v>
+        <v>-0.0482</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.2935</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1395</v>
+        <v>0.2453</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1395</v>
+        <v>-2.8078</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0.6422</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1395</v>
+        <v>-2.1656</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-1.7064</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.2589</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.4476</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1395</v>
+        <v>-1.1014</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.3833</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1395</v>
+        <v>-0.7181</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.2588</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.2588</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.1869</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.4535</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.2665</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.9466</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>4.1252</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1524</v>
+        <v>-0.1426</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8464</v>
+        <v>-3.1331</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6941</v>
+        <v>2.9905</v>
       </c>
       <c r="G8" t="n">
         <v>1.4587</v>
@@ -1078,13 +1078,13 @@
         <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2558</v>
+        <v>-0.246</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1781</v>
+        <v>-0.1086</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4339</v>
+        <v>-0.1374</v>
       </c>
       <c r="V8" t="n">
         <v>0.6982</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4663</v>
+        <v>-0.6409</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1114</v>
+        <v>-0.4639</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3549</v>
+        <v>-0.177</v>
       </c>
       <c r="G9" t="n">
         <v>0.2482</v>
@@ -1156,13 +1156,13 @@
         <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2689</v>
+        <v>-0.4436</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1045</v>
+        <v>-0.248</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3734</v>
+        <v>-0.1956</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2402</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3328</v>
+        <v>-1.0333</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3667</v>
+        <v>-3.5415</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0339</v>
+        <v>2.5082</v>
       </c>
       <c r="G10" t="n">
         <v>0.0519</v>
@@ -1234,13 +1234,13 @@
         <v>2.8748</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.4114</v>
+        <v>-1.1119</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.178</v>
+        <v>-0.3527</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2334</v>
+        <v>-0.7592</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5893</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.361699999999999</v>
+        <v>10.6792</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7119</v>
+        <v>-3.394400000000001</v>
       </c>
       <c r="F11" t="n">
         <v>14.0737</v>
@@ -1312,13 +1312,13 @@
         <v>19.5075</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.961600000000001</v>
+        <v>-6.6441</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.9994</v>
+        <v>-3.6819</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.9623</v>
+        <v>-2.9624</v>
       </c>
       <c r="V11" t="n">
         <v>9.887</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6281</v>
+        <v>2.8344</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6863</v>
+        <v>0.7557</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0582</v>
+        <v>2.0786</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1013</v>
+        <v>2.5478</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2775</v>
+        <v>0.9795</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8238</v>
+        <v>1.5683</v>
       </c>
       <c r="J12" t="n">
-        <v>3.411</v>
+        <v>2.8675</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3321</v>
+        <v>1.6969</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0789</v>
+        <v>1.1706</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3097</v>
+        <v>-0.3197</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0546</v>
+        <v>-0.7174</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7449</v>
+        <v>0.3977</v>
       </c>
       <c r="P12" t="n">
         <v>-0.4107</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0534</v>
+        <v>-2.6694</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6427</v>
+        <v>2.2588</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6439</v>
+        <v>1.1778</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6778</v>
+        <v>0.5577</v>
       </c>
       <c r="U12" t="n">
-        <v>0.966</v>
+        <v>0.6201</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.7063</v>
+        <v>-0.4805</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3573</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>A. MORENO TRUJILLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1746</v>
+        <v>0.8951</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2903</v>
+        <v>-0.521</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4649</v>
+        <v>1.4162</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5478</v>
+        <v>-0.027</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9795</v>
+        <v>-1.1611</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5683</v>
+        <v>1.1342</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8675</v>
+        <v>0.2299</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6969</v>
+        <v>-0.4146</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1706</v>
+        <v>0.6445</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3197</v>
+        <v>-0.2569</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7174</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3977</v>
+        <v>0.4897</v>
       </c>
       <c r="P13" t="n">
         <v>-0.4107</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.6694</v>
+        <v>-2.4641</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2588</v>
+        <v>2.0534</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.482</v>
+        <v>1.3328</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4883</v>
+        <v>0.2943</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0063</v>
+        <v>1.0385</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4805</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MORENO TRUJILLO</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3233</v>
+        <v>0.793</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8348</v>
+        <v>1.0587</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1582</v>
+        <v>-0.2657</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.027</v>
+        <v>3.1013</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1611</v>
+        <v>2.2775</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1342</v>
+        <v>0.8238</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2299</v>
+        <v>3.411</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4146</v>
+        <v>3.3321</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6445</v>
+        <v>0.0789</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2569</v>
+        <v>-0.3097</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-1.0546</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4897</v>
+        <v>0.7449</v>
       </c>
       <c r="P14" t="n">
         <v>-0.4107</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.4641</v>
+        <v>-2.0534</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7609</v>
+        <v>0.8088</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0195</v>
+        <v>0.0502</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7805</v>
+        <v>0.7585</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-2.7063</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4189</v>
+        <v>-0.3491</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4189</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. SIMEUNOVIC</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3986</v>
+        <v>-1.2158</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.1869</v>
+        <v>-2.34</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7883</v>
+        <v>1.1242</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.5927</v>
+        <v>-0.6802</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.3058</v>
+        <v>-0.8434</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7131</v>
+        <v>0.1632</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9863</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.3937</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4073</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.0023</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9121</v>
+        <v>-0.1656</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3057</v>
+        <v>0.1632</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.8214</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-1.4374</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-4.7229</v>
-      </c>
       <c r="R15" t="n">
-        <v>3.2855</v>
+        <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>3.8102</v>
+        <v>0.2858</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2821</v>
+        <v>-0.2248</v>
       </c>
       <c r="U15" t="n">
-        <v>2.5281</v>
+        <v>0.5105</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0249</v>
+        <v>-1.4269</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7817</v>
+        <v>-1.3753</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.8065</v>
+        <v>-0.0516</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2128</v>
+        <v>-0.8922</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.363</v>
+        <v>-0.2661</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1502</v>
+        <v>-0.6261</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1865</v>
+        <v>0.0389</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1076</v>
+        <v>0.0389</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0789</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3993</v>
+        <v>-0.9311</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4706</v>
+        <v>-0.305</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0713</v>
+        <v>-0.6261</v>
       </c>
       <c r="P16" t="n">
         <v>-0.2053</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6274</v>
+        <v>-0.3294</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5254</v>
+        <v>-0.3875</v>
       </c>
       <c r="U16" t="n">
-        <v>0.102</v>
+        <v>0.0581</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.2341</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.5359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>D. SIMEUNOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1339</v>
+        <v>-1.8492</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4446</v>
+        <v>-4.7099</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3108</v>
+        <v>2.8607</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6802</v>
+        <v>-1.5927</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8434</v>
+        <v>-2.3058</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1632</v>
+        <v>0.7131</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.9863</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.3937</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.4073</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0023</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1656</v>
+        <v>-0.9121</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1632</v>
+        <v>0.3057</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.8214</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.4374</v>
+        <v>-4.7229</v>
       </c>
       <c r="R17" t="n">
-        <v>0.616</v>
+        <v>3.2855</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3677</v>
+        <v>2.3595</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3294</v>
+        <v>0.7591</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6971000000000001</v>
+        <v>1.6004</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5455</v>
+        <v>-2.8144</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3753</v>
+        <v>-4.4847</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1702</v>
+        <v>1.6704</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8922</v>
+        <v>-2.5605</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2661</v>
+        <v>-2.3261</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6261</v>
+        <v>-0.2345</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0389</v>
+        <v>-1.9933</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0389</v>
+        <v>-0.9665</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.0268</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9311</v>
+        <v>-0.5672</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.305</v>
+        <v>-1.3596</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6261</v>
+        <v>0.7924</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2053</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-2.6694</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4479</v>
+        <v>0.5675</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3875</v>
+        <v>0.178</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0604</v>
+        <v>0.3895</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.9825</v>
+        <v>-2.8527</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.217</v>
+        <v>-2.1467</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2345</v>
+        <v>-0.706</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5605</v>
+        <v>-4.0399</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3261</v>
+        <v>-2.5586</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2345</v>
+        <v>-1.4813</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9933</v>
+        <v>-2.8757</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9665</v>
+        <v>-1.507</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.0268</v>
+        <v>-1.3686</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5672</v>
+        <v>-1.1642</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3596</v>
+        <v>-1.0516</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7924</v>
+        <v>-0.1127</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.6694</v>
+        <v>-1.2321</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>2.8748</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6006</v>
+        <v>0.8319</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5542</v>
+        <v>0.3019</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0464</v>
+        <v>0.53</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2875</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.6591</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.9466</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4027</v>
+        <v>-3.028</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1927</v>
+        <v>-0.3104</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2099</v>
+        <v>-2.7176</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.0399</v>
+        <v>-0.2128</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5586</v>
+        <v>-0.363</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4813</v>
+        <v>0.1502</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.8757</v>
+        <v>0.1865</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.507</v>
+        <v>0.1076</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3686</v>
+        <v>0.0789</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1642</v>
+        <v>-0.3993</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0516</v>
+        <v>-0.4706</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1127</v>
+        <v>0.0713</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6427</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R20" t="n">
-        <v>2.8748</v>
+        <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.718</v>
+        <v>1.6242</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7441</v>
+        <v>1.4333</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0261</v>
+        <v>0.1909</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2875</v>
+        <v>-4.2341</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6591</v>
+        <v>-0.6982</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.9466</v>
+        <v>-3.5359</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.3621</v>
+        <v>-8.6645</v>
       </c>
       <c r="E21" t="n">
         <v>-14.0736</v>
       </c>
       <c r="F21" t="n">
-        <v>4.7119</v>
+        <v>5.409199999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-4.356199999999999</v>
@@ -2065,19 +2065,19 @@
         <v>2.2109</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2005999999999997</v>
+        <v>0.2006000000000009</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2158</v>
+        <v>0.2158000000000005</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.01519999999999966</v>
+        <v>-0.01519999999999985</v>
       </c>
       <c r="M21" t="n">
         <v>-4.5568</v>
       </c>
       <c r="N21" t="n">
-        <v>-6.782999999999999</v>
+        <v>-6.783</v>
       </c>
       <c r="O21" t="n">
         <v>2.2261</v>
@@ -2092,16 +2092,16 @@
         <v>16.4274</v>
       </c>
       <c r="S21" t="n">
-        <v>7.961600000000001</v>
+        <v>8.658899999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>2.962299999999999</v>
+        <v>2.9622</v>
       </c>
       <c r="U21" t="n">
-        <v>4.9993</v>
+        <v>5.6965</v>
       </c>
       <c r="V21" t="n">
-        <v>-9.886999999999999</v>
+        <v>-9.887</v>
       </c>
       <c r="W21" t="n">
         <v>2.2709</v>
